--- a/output/topology_excel/1160.xlsx
+++ b/output/topology_excel/1160.xlsx
@@ -425,43 +425,58 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>房间ID1</t>
+          <t>房间1</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>房间类型1</t>
+          <t>类型1</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>房间ID2</t>
+          <t>面积1</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>房间类型2</t>
+          <t>房间2</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>类型2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>面积2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>连接类型</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>连接数量</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>连接面积</t>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>length</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>width</t>
         </is>
       </c>
     </row>
@@ -475,168 +490,222 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>386347</v>
+      </c>
+      <c r="D2" t="n">
         <v>2</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
-      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1464</v>
+        <v>101885</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>122</v>
+      </c>
+      <c r="J2" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>101885</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>355</v>
-      </c>
-      <c r="G3" t="n">
-        <v>4260</v>
+        <v>40754</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>60</v>
+      </c>
+      <c r="J3" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
+        <v>40754</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>600</v>
+        <v>80417</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>59</v>
+      </c>
+      <c r="J4" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
+        <v>386347</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>287</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2870</v>
+        <v>97982</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>82</v>
+      </c>
+      <c r="J5" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C6" t="n">
+        <v>386347</v>
+      </c>
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>门/窗</t>
-        </is>
-      </c>
       <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>531</v>
+        <v>80417</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>80</v>
+      </c>
+      <c r="J6" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>386347</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>287</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2583</v>
+        <v>16492</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>76</v>
+      </c>
+      <c r="J7" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -649,23 +718,32 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>386347</v>
+      </c>
+      <c r="D8" t="n">
+        <v>8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>902</v>
+        <v>98340</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>84</v>
+      </c>
+      <c r="J8" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="9">
@@ -678,52 +756,70 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>386347</v>
+      </c>
+      <c r="D9" t="n">
+        <v>7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>603</v>
-      </c>
-      <c r="G9" t="n">
-        <v>8083</v>
+        <v>100010</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>80</v>
+      </c>
+      <c r="J9" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
-      </c>
-      <c r="D10" t="inlineStr">
+        <v>80417</v>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>门/窗</t>
-        </is>
-      </c>
       <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>960</v>
+        <v>32868</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>66</v>
+      </c>
+      <c r="J10" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="11">
@@ -736,23 +832,32 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>386347</v>
+      </c>
+      <c r="D11" t="n">
+        <v>9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>186</v>
-      </c>
-      <c r="G11" t="n">
-        <v>5598</v>
+        <v>29744</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>86</v>
+      </c>
+      <c r="J11" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -765,23 +870,32 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>386347</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>836</v>
+        <v>101885</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>355</v>
+      </c>
+      <c r="J12" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -794,23 +908,32 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>386347</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>124</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1364</v>
+        <v>97982</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>314</v>
+      </c>
+      <c r="J13" t="n">
+        <v>311</v>
       </c>
     </row>
     <row r="14">
@@ -823,23 +946,32 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>386347</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="n">
-        <v>924</v>
+        <v>40754</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>142</v>
+      </c>
+      <c r="J14" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -852,23 +984,32 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>386347</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>358</v>
-      </c>
-      <c r="G15" t="n">
-        <v>3650</v>
+        <v>80417</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>175</v>
+      </c>
+      <c r="J15" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="16">
@@ -881,23 +1022,32 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>386347</v>
+      </c>
+      <c r="D16" t="n">
+        <v>6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" t="n">
-        <v>880</v>
+        <v>16492</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>124</v>
+      </c>
+      <c r="J16" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="17">
@@ -910,226 +1060,298 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>386347</v>
+      </c>
+      <c r="D17" t="n">
+        <v>8</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>118</v>
-      </c>
-      <c r="G17" t="n">
-        <v>3038</v>
+        <v>98340</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>223</v>
+      </c>
+      <c r="J17" t="n">
+        <v>155</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>10</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>386347</v>
+      </c>
+      <c r="D18" t="n">
+        <v>7</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1122</v>
+        <v>100010</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>156</v>
+      </c>
+      <c r="J18" t="n">
+        <v>118</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C19" t="n">
+        <v>386347</v>
+      </c>
+      <c r="D19" t="n">
+        <v>9</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Hallway</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>29744</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>169</v>
+      </c>
+      <c r="J19" t="n">
         <v>10</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>198</v>
-      </c>
-      <c r="G19" t="n">
-        <v>3366</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
+        <v>101885</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" t="n">
-        <v>860</v>
+        <v>40754</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>287</v>
+      </c>
+      <c r="J20" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>9</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
+        <v>97982</v>
+      </c>
+      <c r="D21" t="n">
+        <v>7</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>169</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1690</v>
+        <v>100010</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>170</v>
+      </c>
+      <c r="J21" t="n">
+        <v>146</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
+        <v>97982</v>
+      </c>
+      <c r="D22" t="n">
+        <v>6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>142</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1704</v>
+        <v>16492</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>145</v>
+      </c>
+      <c r="J22" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>40754</v>
+      </c>
+      <c r="D23" t="n">
+        <v>5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>54</v>
-      </c>
-      <c r="G23" t="n">
-        <v>648</v>
+        <v>80417</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>287</v>
+      </c>
+      <c r="J23" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>7</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>80417</v>
+      </c>
+      <c r="D24" t="n">
+        <v>8</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>158</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1422</v>
+        <v>98340</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>148</v>
+      </c>
+      <c r="J24" t="n">
+        <v>83</v>
       </c>
     </row>
     <row r="25">
@@ -1142,23 +1364,32 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>8</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>80417</v>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>137</v>
-      </c>
-      <c r="G25" t="n">
-        <v>1507</v>
+        <v>32868</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>198</v>
+      </c>
+      <c r="J25" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="26">
@@ -1171,23 +1402,32 @@
         </is>
       </c>
       <c r="C26" t="n">
+        <v>16492</v>
+      </c>
+      <c r="D26" t="n">
         <v>7</v>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
-      </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>61</v>
-      </c>
-      <c r="G26" t="n">
-        <v>732</v>
+        <v>100010</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>145</v>
+      </c>
+      <c r="J26" t="n">
+        <v>73</v>
       </c>
     </row>
     <row r="27">
@@ -1200,23 +1440,32 @@
         </is>
       </c>
       <c r="C27" t="n">
+        <v>100010</v>
+      </c>
+      <c r="D27" t="n">
         <v>8</v>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
-      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F27" t="n">
+        <v>98340</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>189</v>
+      </c>
+      <c r="J27" t="n">
         <v>10</v>
-      </c>
-      <c r="G27" t="n">
-        <v>1890</v>
       </c>
     </row>
     <row r="28">
@@ -1229,23 +1478,32 @@
         </is>
       </c>
       <c r="C28" t="n">
+        <v>100010</v>
+      </c>
+      <c r="D28" t="n">
         <v>9</v>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Hallway</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F28" t="n">
+        <v>29744</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
         <v>176</v>
       </c>
-      <c r="G28" t="n">
-        <v>1936</v>
+      <c r="J28" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="29">
@@ -1258,23 +1516,32 @@
         </is>
       </c>
       <c r="C29" t="n">
+        <v>98340</v>
+      </c>
+      <c r="D29" t="n">
         <v>9</v>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Hallway</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F29" t="n">
+        <v>29744</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
         <v>176</v>
       </c>
-      <c r="G29" t="n">
-        <v>1584</v>
+      <c r="J29" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="30">
@@ -1287,23 +1554,32 @@
         </is>
       </c>
       <c r="C30" t="n">
+        <v>98340</v>
+      </c>
+      <c r="D30" t="n">
         <v>10</v>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F30" t="n">
+        <v>32868</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n">
         <v>166</v>
       </c>
-      <c r="G30" t="n">
-        <v>1826</v>
+      <c r="J30" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/1160.xlsx
+++ b/output/topology_excel/1160.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,7 +505,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -543,7 +543,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -581,7 +581,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -619,7 +619,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -695,7 +695,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -733,7 +733,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -771,7 +771,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -809,7 +809,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -847,7 +847,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -933,7 +933,7 @@
         <v>314</v>
       </c>
       <c r="J13" t="n">
-        <v>311</v>
+        <v>301</v>
       </c>
     </row>
     <row r="14">
@@ -1120,10 +1120,10 @@
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>156</v>
+        <v>106</v>
       </c>
       <c r="J18" t="n">
-        <v>118</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19">
@@ -1215,15 +1215,15 @@
         <v>97982</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>100010</v>
+        <v>16492</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1234,10 +1234,10 @@
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="J21" t="n">
-        <v>146</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22">
@@ -1253,15 +1253,15 @@
         <v>97982</v>
       </c>
       <c r="D22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>16492</v>
+        <v>100010</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="J22" t="n">
-        <v>64</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23">
@@ -1443,15 +1443,15 @@
         <v>100010</v>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>98340</v>
+        <v>29744</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1462,15 +1462,15 @@
         <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="J27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>100010</v>
+        <v>98340</v>
       </c>
       <c r="D28" t="n">
         <v>9</v>
@@ -1503,7 +1503,7 @@
         <v>176</v>
       </c>
       <c r="J28" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29">
@@ -1519,15 +1519,15 @@
         <v>98340</v>
       </c>
       <c r="D29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>29744</v>
+        <v>32868</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1538,47 +1538,9 @@
         <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="J29" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>8</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>98340</v>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>32868</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H30" t="n">
-        <v>1</v>
-      </c>
-      <c r="I30" t="n">
-        <v>166</v>
-      </c>
-      <c r="J30" t="n">
         <v>11</v>
       </c>
     </row>

--- a/output/topology_excel/1160.xlsx
+++ b/output/topology_excel/1160.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,10 +462,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -484,10 +484,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -506,10 +506,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -542,18 +542,18 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -564,18 +564,18 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="F7" t="n">
         <v>11</v>
@@ -594,10 +594,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -608,7 +608,7 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F8" t="n">
         <v>11</v>
@@ -616,10 +616,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -630,15 +630,15 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="F9" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B10" t="n">
         <v>10</v>
@@ -652,10 +652,10 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="F10" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -663,21 +663,21 @@
         <v>1</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Door</t>
+          <t>Wall</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="F11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
@@ -685,7 +685,7 @@
         <v>1</v>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -696,15 +696,15 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>355</v>
+        <v>303</v>
       </c>
       <c r="F12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B13" t="n">
         <v>3</v>
@@ -718,15 +718,15 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>314</v>
+        <v>355</v>
       </c>
       <c r="F13" t="n">
-        <v>301</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B14" t="n">
         <v>4</v>
@@ -740,18 +740,18 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>142</v>
+        <v>211</v>
       </c>
       <c r="F14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>175</v>
+        <v>142</v>
       </c>
       <c r="F15" t="n">
         <v>12</v>
@@ -770,10 +770,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B16" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -784,18 +784,18 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>124</v>
+        <v>223</v>
       </c>
       <c r="F16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B17" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -806,18 +806,18 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>223</v>
+        <v>287</v>
       </c>
       <c r="F17" t="n">
-        <v>155</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="F18" t="n">
         <v>11</v>
@@ -836,10 +836,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -850,18 +850,18 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="F19" t="n">
-        <v>10</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -872,18 +872,18 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>287</v>
+        <v>158</v>
       </c>
       <c r="F20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -897,15 +897,15 @@
         <v>145</v>
       </c>
       <c r="F21" t="n">
-        <v>64</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B22" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -916,18 +916,18 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>158</v>
+        <v>106</v>
       </c>
       <c r="F22" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -938,18 +938,18 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>287</v>
+        <v>176</v>
       </c>
       <c r="F23" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -960,18 +960,18 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="F24" t="n">
-        <v>83</v>
+        <v>155</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B25" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -982,10 +982,10 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>198</v>
+        <v>72</v>
       </c>
       <c r="F25" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26">
@@ -993,7 +993,7 @@
         <v>6</v>
       </c>
       <c r="B26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1004,18 +1004,18 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="F26" t="n">
-        <v>73</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1029,15 +1029,15 @@
         <v>176</v>
       </c>
       <c r="F27" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B28" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1048,32 +1048,186 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="F28" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" t="n">
+        <v>9</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>124</v>
+      </c>
+      <c r="F29" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
         <v>8</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B30" t="n">
+        <v>14</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>198</v>
+      </c>
+      <c r="F30" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>9</v>
+      </c>
+      <c r="B31" t="n">
+        <v>13</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>175</v>
+      </c>
+      <c r="F31" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>9</v>
+      </c>
+      <c r="B32" t="n">
         <v>10</v>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" t="n">
-        <v>166</v>
-      </c>
-      <c r="F29" t="n">
-        <v>11</v>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>169</v>
+      </c>
+      <c r="F32" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>11</v>
+      </c>
+      <c r="B33" t="n">
+        <v>13</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>287</v>
+      </c>
+      <c r="F33" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>1</v>
+      </c>
+      <c r="B34" t="n">
+        <v>2</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>228</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2</v>
+      </c>
+      <c r="B35" t="n">
+        <v>9</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
+        <v>169</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>8</v>
+      </c>
+      <c r="B36" t="n">
+        <v>13</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>204</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/1160.xlsx
+++ b/output/topology_excel/1160.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Length_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Width_2</t>
         </is>
       </c>
     </row>
@@ -481,6 +491,8 @@
       <c r="F2" t="n">
         <v>12</v>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -503,6 +515,8 @@
       <c r="F3" t="n">
         <v>10</v>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -525,6 +539,8 @@
       <c r="F4" t="n">
         <v>9</v>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -547,6 +563,8 @@
       <c r="F5" t="n">
         <v>12</v>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -569,6 +587,8 @@
       <c r="F6" t="n">
         <v>11</v>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -591,6 +611,8 @@
       <c r="F7" t="n">
         <v>11</v>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -613,6 +635,8 @@
       <c r="F8" t="n">
         <v>11</v>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -635,6 +659,8 @@
       <c r="F9" t="n">
         <v>17</v>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -657,6 +683,8 @@
       <c r="F10" t="n">
         <v>10</v>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -679,6 +707,8 @@
       <c r="F11" t="n">
         <v>11</v>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -701,6 +731,8 @@
       <c r="F12" t="n">
         <v>11</v>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -723,6 +755,8 @@
       <c r="F13" t="n">
         <v>12</v>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -745,6 +779,8 @@
       <c r="F14" t="n">
         <v>11</v>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -767,6 +803,8 @@
       <c r="F15" t="n">
         <v>12</v>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -789,6 +827,8 @@
       <c r="F16" t="n">
         <v>9</v>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -811,6 +851,8 @@
       <c r="F17" t="n">
         <v>10</v>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -833,6 +875,8 @@
       <c r="F18" t="n">
         <v>11</v>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -847,13 +891,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="F19" t="n">
-        <v>64</v>
+        <v>10</v>
+      </c>
+      <c r="G19" t="n">
+        <v>54</v>
+      </c>
+      <c r="H19" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="20">
@@ -877,6 +927,8 @@
       <c r="F20" t="n">
         <v>9</v>
       </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -891,13 +943,19 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>145</v>
+        <v>61</v>
       </c>
       <c r="F21" t="n">
-        <v>73</v>
+        <v>12</v>
+      </c>
+      <c r="G21" t="n">
+        <v>133</v>
+      </c>
+      <c r="H21" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="22">
@@ -921,6 +979,8 @@
       <c r="F22" t="n">
         <v>11</v>
       </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -943,6 +1003,8 @@
       <c r="F23" t="n">
         <v>11</v>
       </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -957,13 +1019,19 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="F24" t="n">
-        <v>155</v>
+        <v>11</v>
+      </c>
+      <c r="G24" t="n">
+        <v>144</v>
+      </c>
+      <c r="H24" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="25">
@@ -987,6 +1055,8 @@
       <c r="F25" t="n">
         <v>11</v>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1009,6 +1079,8 @@
       <c r="F26" t="n">
         <v>11</v>
       </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1031,6 +1103,8 @@
       <c r="F27" t="n">
         <v>9</v>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1053,6 +1127,8 @@
       <c r="F28" t="n">
         <v>11</v>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1075,6 +1151,8 @@
       <c r="F29" t="n">
         <v>11</v>
       </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1097,6 +1175,8 @@
       <c r="F30" t="n">
         <v>17</v>
       </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1119,6 +1199,8 @@
       <c r="F31" t="n">
         <v>12</v>
       </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1141,6 +1223,8 @@
       <c r="F32" t="n">
         <v>10</v>
       </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1163,6 +1247,8 @@
       <c r="F33" t="n">
         <v>9</v>
       </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1185,6 +1271,8 @@
       <c r="F34" t="n">
         <v>1</v>
       </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1207,6 +1295,8 @@
       <c r="F35" t="n">
         <v>1</v>
       </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1229,6 +1319,8 @@
       <c r="F36" t="n">
         <v>1</v>
       </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
